--- a/artfynd/A 1876-2021 artfynd.xlsx
+++ b/artfynd/A 1876-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117818235</v>
+        <v>117818242</v>
       </c>
       <c r="B2" t="n">
-        <v>56549</v>
+        <v>57656</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>102976</v>
+        <v>103015</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117818245</v>
+        <v>117818235</v>
       </c>
       <c r="B3" t="n">
-        <v>57768</v>
+        <v>56549</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,25 +811,25 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>103018</v>
+        <v>102976</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Svartvit flugsnappare</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Ficedula hypoleuca</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Pallas, 1764)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -841,7 +841,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -923,10 +923,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>117818242</v>
+        <v>117818245</v>
       </c>
       <c r="B4" t="n">
-        <v>57656</v>
+        <v>57768</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
@@ -935,25 +935,25 @@
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>103015</v>
+        <v>103018</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Svartvit flugsnappare</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Ficedula hypoleuca</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Pallas, 1764)</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
@@ -965,7 +965,7 @@
       <c r="L4" t="inlineStr"/>
       <c r="M4" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>spel/sång</t>
         </is>
       </c>
       <c r="N4" t="inlineStr"/>

--- a/artfynd/A 1876-2021 artfynd.xlsx
+++ b/artfynd/A 1876-2021 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>117818242</v>
+        <v>117818235</v>
       </c>
       <c r="B2" t="n">
-        <v>57656</v>
+        <v>56550</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -687,20 +687,20 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>103015</v>
+        <v>102976</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Kungsfågel</t>
+          <t>Tornseglare</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Regulus regulus</t>
+          <t>Apus apus</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
@@ -717,7 +717,7 @@
       <c r="L2" t="inlineStr"/>
       <c r="M2" t="inlineStr">
         <is>
-          <t>födosökande</t>
+          <t>förbiflygande</t>
         </is>
       </c>
       <c r="N2" t="inlineStr"/>
@@ -762,7 +762,7 @@
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
@@ -772,7 +772,7 @@
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>13:45</t>
+          <t>13:30</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -799,10 +799,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>117818235</v>
+        <v>117818242</v>
       </c>
       <c r="B3" t="n">
-        <v>56549</v>
+        <v>57657</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -811,20 +811,20 @@
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>EN</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>102976</v>
+        <v>103015</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Tornseglare</t>
+          <t>Kungsfågel</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Apus apus</t>
+          <t>Regulus regulus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
@@ -841,7 +841,7 @@
       <c r="L3" t="inlineStr"/>
       <c r="M3" t="inlineStr">
         <is>
-          <t>förbiflygande</t>
+          <t>födosökande</t>
         </is>
       </c>
       <c r="N3" t="inlineStr"/>
@@ -886,7 +886,7 @@
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
@@ -896,7 +896,7 @@
       </c>
       <c r="AB3" t="inlineStr">
         <is>
-          <t>13:30</t>
+          <t>13:45</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -926,7 +926,7 @@
         <v>117818245</v>
       </c>
       <c r="B4" t="n">
-        <v>57768</v>
+        <v>57769</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
